--- a/docs/PHIẾU ĐĂNG KÝ TĂNG CA.xlsx
+++ b/docs/PHIẾU ĐĂNG KÝ TĂNG CA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/620493bafd38e3c2/0. Production/9. KHSX/00. Claude app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hansungbolt-overtime\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_74FB7060CEF851C1F92A40F5228DD7E8818B421C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67437BCF-876B-43EF-BA68-883DA761D261}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79243FE2-8D77-4E84-956E-E1F0FB786D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-50" yWindow="-50" windowWidth="38500" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HD" sheetId="9" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="171">
   <si>
     <t>STT
 No.</t>
@@ -1443,8 +1443,44 @@
     <t>M3</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Total: 32 MC </t>
+    <t>CT-01~06
+(6EA)</t>
+  </si>
+  <si>
+    <t>CUTTING</t>
+  </si>
+  <si>
+    <t>TAE HUNG</t>
+  </si>
+  <si>
+    <t>M3-M6</t>
+  </si>
+  <si>
+    <t>Quy cách</t>
+  </si>
+  <si>
+    <t>Số lượng sản xuất 1 tiếng</t>
+  </si>
+  <si>
+    <t>VỆ SINH
+MÁY LẠNH</t>
+  </si>
+  <si>
+    <t>Dự kiến
+4 ngày</t>
+  </si>
+  <si>
+    <t>9/14 EA</t>
+  </si>
+  <si>
+    <t>RL-24</t>
+  </si>
+  <si>
+    <t>FUJIU MACHINERY FACTORY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Total: 33 MC </t>
     </r>
     <r>
       <rPr>
@@ -1455,38 +1491,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>( 25 RL &amp; 7 SM)</t>
-    </r>
-  </si>
-  <si>
-    <t>CT-01~06
-(6EA)</t>
-  </si>
-  <si>
-    <t>CUTTING</t>
-  </si>
-  <si>
-    <t>TAE HUNG</t>
-  </si>
-  <si>
-    <t>M3-M6</t>
-  </si>
-  <si>
-    <t>Quy cách</t>
-  </si>
-  <si>
-    <t>Số lượng sản xuất 1 tiếng</t>
-  </si>
-  <si>
-    <t>VỆ SINH
-MÁY LẠNH</t>
-  </si>
-  <si>
-    <t>Dự kiến
-4 ngày</t>
-  </si>
-  <si>
-    <t>9/14 EA</t>
+      <t>( 26 RL &amp; 7 SM)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1524,7 +1530,7 @@
     <numFmt numFmtId="189" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;\-#,##0.00"/>
     <numFmt numFmtId="190" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;\-#,##0.00"/>
     <numFmt numFmtId="191" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="193" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="192" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
   <fonts count="130">
     <font>
@@ -3754,7 +3760,7 @@
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="193" fontId="103" fillId="0" borderId="0" xfId="277" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="103" fillId="0" borderId="0" xfId="277" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3882,9 +3888,60 @@
     <xf numFmtId="0" fontId="106" fillId="50" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="108" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="108" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="108" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="108" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="108" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="108" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3894,12 +3951,6 @@
     <xf numFmtId="0" fontId="107" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3909,12 +3960,6 @@
     <xf numFmtId="0" fontId="122" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3926,45 +3971,6 @@
     </xf>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="108" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="108" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="108" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="108" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="108" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="108" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4312,8 +4318,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5206512" y="5679097"/>
-          <a:ext cx="3023822" cy="817440"/>
+          <a:off x="5466862" y="5726722"/>
+          <a:ext cx="3169872" cy="814265"/>
           <a:chOff x="6391275" y="9576970"/>
           <a:chExt cx="1472223" cy="1310105"/>
         </a:xfrm>
@@ -4462,8 +4468,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="81328" y="5686425"/>
-          <a:ext cx="4430347" cy="810113"/>
+          <a:off x="87678" y="5734050"/>
+          <a:ext cx="4649422" cy="806938"/>
           <a:chOff x="85725" y="9553575"/>
           <a:chExt cx="4222768" cy="1333500"/>
         </a:xfrm>
@@ -5231,8 +5237,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5425587" y="4174147"/>
-          <a:ext cx="3023822" cy="817440"/>
+          <a:off x="5689112" y="4177322"/>
+          <a:ext cx="3169872" cy="814265"/>
           <a:chOff x="6391275" y="9576970"/>
           <a:chExt cx="1472223" cy="1310105"/>
         </a:xfrm>
@@ -5381,8 +5387,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="81328" y="4181475"/>
-          <a:ext cx="4649422" cy="810113"/>
+          <a:off x="87678" y="4184650"/>
+          <a:ext cx="4871672" cy="806938"/>
           <a:chOff x="85725" y="9553575"/>
           <a:chExt cx="4222768" cy="1333500"/>
         </a:xfrm>
@@ -6435,104 +6441,104 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:T22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="12" customWidth="1"/>
-    <col min="7" max="8" width="10.140625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="12" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="12" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" style="12" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="12" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="1.1796875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="7.1796875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="10.1796875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="12" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="5.26953125" style="12" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="12" customWidth="1"/>
+    <col min="14" max="16384" width="9.1796875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15.75">
+    <row r="1" spans="2:20" ht="15.5">
       <c r="B1" s="11"/>
     </row>
-    <row r="2" spans="2:20" ht="15.75">
+    <row r="2" spans="2:20" ht="15.5">
       <c r="B2" s="11"/>
     </row>
-    <row r="3" spans="2:20" ht="15.75">
+    <row r="3" spans="2:20" ht="15.5">
       <c r="B3" s="13"/>
     </row>
     <row r="4" spans="2:20" s="14" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
       <c r="O4" s="26"/>
     </row>
-    <row r="5" spans="2:20" s="14" customFormat="1" ht="30.95" customHeight="1">
-      <c r="B5" s="53" t="s">
+    <row r="5" spans="2:20" s="14" customFormat="1" ht="31" customHeight="1">
+      <c r="B5" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="53" t="s">
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="72"/>
     </row>
     <row r="6" spans="2:20" ht="9" customHeight="1"/>
-    <row r="7" spans="2:20" ht="38.450000000000003" customHeight="1">
-      <c r="B7" s="56" t="s">
+    <row r="7" spans="2:20" ht="38.5" customHeight="1">
+      <c r="B7" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="D7" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56" t="s">
+      <c r="E7" s="68"/>
+      <c r="F7" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56" t="s">
+      <c r="G7" s="68"/>
+      <c r="H7" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="56" t="s">
+      <c r="K7" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="56" t="s">
+      <c r="L7" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="56" t="s">
+      <c r="M7" s="68" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:20" ht="42.6" customHeight="1">
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
+    <row r="8" spans="2:20" ht="42.65" customHeight="1">
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
       <c r="D8" s="15" t="s">
         <v>56</v>
       </c>
@@ -6545,28 +6551,28 @@
       <c r="G8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-    </row>
-    <row r="9" spans="2:20" ht="32.1" customHeight="1">
-      <c r="B9" s="67">
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+    </row>
+    <row r="9" spans="2:20" ht="32.15" customHeight="1">
+      <c r="B9" s="53">
         <v>1</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
       <c r="H9" s="15" t="s">
         <v>36</v>
       </c>
@@ -6581,13 +6587,13 @@
       <c r="L9" s="17"/>
       <c r="M9" s="27"/>
     </row>
-    <row r="10" spans="2:20" ht="32.1" customHeight="1">
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
+    <row r="10" spans="2:20" ht="32.15" customHeight="1">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="15" t="s">
         <v>73</v>
       </c>
@@ -6602,13 +6608,13 @@
       <c r="L10" s="17"/>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" spans="2:20" ht="32.1" customHeight="1">
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
+    <row r="11" spans="2:20" ht="32.15" customHeight="1">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="15" t="s">
         <v>28</v>
       </c>
@@ -6623,13 +6629,13 @@
       <c r="L11" s="17"/>
       <c r="M11" s="27"/>
     </row>
-    <row r="12" spans="2:20" ht="32.1" customHeight="1">
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
+    <row r="12" spans="2:20" ht="32.15" customHeight="1">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="15" t="s">
         <v>76</v>
       </c>
@@ -6644,13 +6650,13 @@
       <c r="L12" s="17"/>
       <c r="M12" s="27"/>
     </row>
-    <row r="13" spans="2:20" ht="32.1" customHeight="1">
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
+    <row r="13" spans="2:20" ht="32.15" customHeight="1">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
       <c r="H13" s="15" t="s">
         <v>79</v>
       </c>
@@ -6665,7 +6671,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="27"/>
     </row>
-    <row r="14" spans="2:20" ht="32.1" customHeight="1">
+    <row r="14" spans="2:20" ht="32.15" customHeight="1">
       <c r="B14" s="17">
         <v>2</v>
       </c>
@@ -6694,7 +6700,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="27"/>
     </row>
-    <row r="15" spans="2:20" ht="32.1" customHeight="1">
+    <row r="15" spans="2:20" ht="32.15" customHeight="1">
       <c r="B15" s="17">
         <v>3</v>
       </c>
@@ -6730,75 +6736,67 @@
       </c>
     </row>
     <row r="17" spans="2:13" s="11" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
     </row>
     <row r="18" spans="2:13" s="11" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
     </row>
     <row r="19" spans="2:13" s="11" customFormat="1" ht="3.75" customHeight="1">
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="56"/>
     </row>
     <row r="20" spans="2:13" s="11" customFormat="1" ht="33" customHeight="1">
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="56"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1"/>
     <row r="22" spans="2:13" ht="5.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="B19:M20"/>
-    <mergeCell ref="B17:M18"/>
-    <mergeCell ref="G9:G13"/>
-    <mergeCell ref="F9:F13"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="C9:C13"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
@@ -6812,6 +6810,14 @@
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="B19:M20"/>
+    <mergeCell ref="B17:M18"/>
+    <mergeCell ref="G9:G13"/>
+    <mergeCell ref="F9:F13"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="C9:C13"/>
   </mergeCells>
   <phoneticPr fontId="118" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6829,106 +6835,106 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="12" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="12" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="12" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" style="12" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="12" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="1.1796875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="12" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="5.26953125" style="12" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="12" customWidth="1"/>
+    <col min="14" max="16384" width="9.1796875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75">
+    <row r="1" spans="1:22" ht="15.5">
       <c r="B1" s="11"/>
     </row>
-    <row r="2" spans="1:22" ht="15.75">
+    <row r="2" spans="1:22" ht="15.5">
       <c r="B2" s="11"/>
     </row>
-    <row r="3" spans="1:22" ht="15.75">
+    <row r="3" spans="1:22" ht="15.5">
       <c r="B3" s="13"/>
     </row>
-    <row r="4" spans="1:22" s="14" customFormat="1" ht="65.45" customHeight="1">
-      <c r="B4" s="52" t="s">
+    <row r="4" spans="1:22" s="14" customFormat="1" ht="65.5" customHeight="1">
+      <c r="B4" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
     </row>
     <row r="5" spans="1:22" s="14" customFormat="1" ht="38.25" customHeight="1">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="53" t="s">
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="72"/>
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:22" ht="9" customHeight="1"/>
-    <row r="7" spans="1:22" ht="38.450000000000003" customHeight="1">
-      <c r="B7" s="56" t="s">
+    <row r="7" spans="1:22" ht="38.5" customHeight="1">
+      <c r="B7" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="D7" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56" t="s">
+      <c r="E7" s="68"/>
+      <c r="F7" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56" t="s">
+      <c r="G7" s="68"/>
+      <c r="H7" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="56" t="s">
+      <c r="K7" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="56" t="s">
+      <c r="L7" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="56" t="s">
+      <c r="M7" s="68" t="s">
         <v>5</v>
       </c>
       <c r="P7" s="26"/>
     </row>
-    <row r="8" spans="1:22" ht="42.6" customHeight="1">
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
+    <row r="8" spans="1:22" ht="42.65" customHeight="1">
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
       <c r="D8" s="15" t="s">
         <v>56</v>
       </c>
@@ -6941,29 +6947,29 @@
       <c r="G8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
       <c r="O8" s="26"/>
     </row>
-    <row r="9" spans="1:22" ht="24.95" customHeight="1">
-      <c r="B9" s="58" t="s">
+    <row r="9" spans="1:22" ht="25" customHeight="1">
+      <c r="B9" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="60"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="75"/>
     </row>
     <row r="10" spans="1:22" ht="28.5" customHeight="1">
       <c r="A10" s="20"/>
@@ -6981,17 +6987,17 @@
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="29"/>
-      <c r="H10" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="I10" s="65" t="s">
-        <v>168</v>
+      <c r="H10" s="76" t="s">
+        <v>165</v>
+      </c>
+      <c r="I10" s="78" t="s">
+        <v>167</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="21"/>
       <c r="L10" s="25"/>
-      <c r="M10" s="65" t="s">
-        <v>167</v>
+      <c r="M10" s="78" t="s">
+        <v>166</v>
       </c>
       <c r="P10" s="23"/>
     </row>
@@ -7011,12 +7017,12 @@
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="66"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="79"/>
       <c r="J11" s="22"/>
       <c r="K11" s="21"/>
       <c r="L11" s="25"/>
-      <c r="M11" s="66"/>
+      <c r="M11" s="79"/>
       <c r="P11" s="23"/>
     </row>
     <row r="12" spans="1:22" ht="71.25" customHeight="1">
@@ -7028,73 +7034,67 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="11" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
     </row>
     <row r="14" spans="1:22" s="11" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
     </row>
     <row r="15" spans="1:22" s="11" customFormat="1" ht="3.75" customHeight="1">
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="61"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
     </row>
     <row r="16" spans="1:22" s="11" customFormat="1" ht="33" customHeight="1">
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="61"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
     </row>
     <row r="17" ht="17.25" customHeight="1"/>
     <row r="18" ht="5.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B15:M16"/>
-    <mergeCell ref="B13:M14"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="I10:I11"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="H5:M5"/>
@@ -7108,6 +7108,12 @@
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B15:M16"/>
+    <mergeCell ref="B13:M14"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="I10:I11"/>
   </mergeCells>
   <phoneticPr fontId="118" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7121,21 +7127,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="61.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="61.26953125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="46.5">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="46">
+      <c r="A1" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
     </row>
     <row r="2" spans="1:3" s="5" customFormat="1">
       <c r="A2" s="4" t="s">
@@ -7148,7 +7154,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="3" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -7159,7 +7165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="4" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -7170,7 +7176,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="5" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A5" s="7">
         <v>3</v>
       </c>
@@ -7181,7 +7187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="6" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A6" s="7">
         <v>4</v>
       </c>
@@ -7192,7 +7198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="7" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -7203,7 +7209,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="8" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A8" s="7">
         <v>6</v>
       </c>
@@ -7214,7 +7220,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="9" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A9" s="7">
         <v>7</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="10" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A10" s="7">
         <v>8</v>
       </c>
@@ -7236,7 +7242,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="11" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A11" s="7">
         <v>9</v>
       </c>
@@ -7247,7 +7253,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="12" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A12" s="7">
         <v>10</v>
       </c>
@@ -7258,7 +7264,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="13" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A13" s="7">
         <v>11</v>
       </c>
@@ -7269,7 +7275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="14" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A14" s="7">
         <v>12</v>
       </c>
@@ -7280,7 +7286,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="15" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A15" s="7">
         <v>13</v>
       </c>
@@ -7291,7 +7297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="16" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A16" s="7">
         <v>14</v>
       </c>
@@ -7307,7 +7313,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="18" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -7318,7 +7324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="19" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A19" s="7">
         <v>2</v>
       </c>
@@ -7329,7 +7335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="20" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A20" s="7">
         <v>3</v>
       </c>
@@ -7340,7 +7346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="21" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A21" s="7">
         <v>4</v>
       </c>
@@ -7351,7 +7357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="22" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A22" s="7">
         <v>5</v>
       </c>
@@ -7362,7 +7368,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="23" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A23" s="7">
         <v>6</v>
       </c>
@@ -7373,7 +7379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="24" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A24" s="7">
         <v>7</v>
       </c>
@@ -7384,7 +7390,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="25" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A25" s="7">
         <v>8</v>
       </c>
@@ -7395,7 +7401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="26" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A26" s="7">
         <v>9</v>
       </c>
@@ -7406,7 +7412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="27" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A27" s="7">
         <v>10</v>
       </c>
@@ -7417,7 +7423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="8" customFormat="1" ht="15.75">
+    <row r="28" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A28" s="7">
         <v>11</v>
       </c>
@@ -7466,22 +7472,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEB8C6C-2C8B-4474-AB53-38C0EB5023E6}">
-  <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="30" customWidth="1"/>
-    <col min="2" max="3" width="12.5703125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="30" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" style="30" customWidth="1"/>
+    <col min="2" max="3" width="12.54296875" style="30" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.81640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" style="30" customWidth="1"/>
     <col min="7" max="7" width="12" style="31" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="31" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" style="30" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="30"/>
+    <col min="8" max="8" width="28.54296875" style="31" customWidth="1"/>
+    <col min="9" max="9" width="15.81640625" style="30" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.5" thickBot="1"/>
-    <row r="2" spans="1:9" ht="44.25" thickBot="1">
+    <row r="1" spans="1:9" ht="13" thickBot="1"/>
+    <row r="2" spans="1:9" ht="44" thickBot="1">
       <c r="A2" s="80" t="s">
         <v>85</v>
       </c>
@@ -7494,7 +7500,7 @@
       <c r="H2" s="81"/>
       <c r="I2" s="82"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1">
+    <row r="3" spans="1:9" ht="15" thickBot="1">
       <c r="A3" s="83" t="s">
         <v>86</v>
       </c>
@@ -7502,7 +7508,7 @@
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
     </row>
-    <row r="4" spans="1:9" s="37" customFormat="1" ht="17.25">
+    <row r="4" spans="1:9" s="37" customFormat="1" ht="17">
       <c r="A4" s="33" t="s">
         <v>87</v>
       </c>
@@ -7510,7 +7516,7 @@
         <v>88</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>89</v>
@@ -7525,7 +7531,7 @@
         <v>92</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I4" s="36" t="s">
         <v>93</v>
@@ -7582,7 +7588,7 @@
         <v>45</v>
       </c>
       <c r="H6" s="48">
-        <f t="shared" ref="H6:H43" si="0">G6*60</f>
+        <f t="shared" ref="H6:H44" si="0">G6*60</f>
         <v>2700</v>
       </c>
       <c r="I6" s="42"/>
@@ -8160,7 +8166,7 @@
       <c r="H27" s="85"/>
       <c r="I27" s="86"/>
     </row>
-    <row r="28" spans="1:9" ht="31.5">
+    <row r="28" spans="1:9" ht="31">
       <c r="A28" s="38">
         <v>1</v>
       </c>
@@ -8188,7 +8194,7 @@
       </c>
       <c r="I28" s="42"/>
     </row>
-    <row r="29" spans="1:9" ht="31.5">
+    <row r="29" spans="1:9" ht="31">
       <c r="A29" s="38">
         <v>2</v>
       </c>
@@ -8216,7 +8222,7 @@
       </c>
       <c r="I29" s="42"/>
     </row>
-    <row r="30" spans="1:9" ht="31.5">
+    <row r="30" spans="1:9" ht="31">
       <c r="A30" s="38">
         <v>3</v>
       </c>
@@ -8244,7 +8250,7 @@
       </c>
       <c r="I30" s="42"/>
     </row>
-    <row r="31" spans="1:9" ht="31.5">
+    <row r="31" spans="1:9" ht="31">
       <c r="A31" s="38">
         <v>4</v>
       </c>
@@ -8272,7 +8278,7 @@
       </c>
       <c r="I31" s="42"/>
     </row>
-    <row r="32" spans="1:9" ht="31.5">
+    <row r="32" spans="1:9" ht="31">
       <c r="A32" s="38">
         <v>5</v>
       </c>
@@ -8300,7 +8306,7 @@
       </c>
       <c r="I32" s="42"/>
     </row>
-    <row r="33" spans="1:9" ht="31.5">
+    <row r="33" spans="1:9" ht="31">
       <c r="A33" s="38">
         <v>6</v>
       </c>
@@ -8328,96 +8334,96 @@
       </c>
       <c r="I33" s="42"/>
     </row>
-    <row r="34" spans="1:9" ht="31.5">
+    <row r="34" spans="1:9" ht="36" customHeight="1">
       <c r="A34" s="38">
         <v>7</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="D34" s="39" t="s">
         <v>137</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F34" s="39" t="s">
         <v>6</v>
       </c>
       <c r="G34" s="39">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="H34" s="48">
         <f t="shared" si="0"/>
-        <v>21000</v>
+        <v>3600</v>
       </c>
       <c r="I34" s="42"/>
     </row>
-    <row r="35" spans="1:9" ht="31.5">
+    <row r="35" spans="1:9" ht="31">
       <c r="A35" s="38">
         <v>8</v>
       </c>
-      <c r="B35" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>139</v>
+      <c r="B35" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>158</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="G35" s="39">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="H35" s="48">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="I35" s="42"/>
     </row>
-    <row r="36" spans="1:9" ht="31.5">
+    <row r="36" spans="1:9" ht="31">
       <c r="A36" s="38">
         <v>9</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D36" s="39" t="s">
         <v>154</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G36" s="39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H36" s="48">
         <f t="shared" si="0"/>
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="I36" s="42"/>
     </row>
-    <row r="37" spans="1:9" ht="31.5">
+    <row r="37" spans="1:9" ht="31">
       <c r="A37" s="38">
         <v>10</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="C37" s="39" t="s">
         <v>143</v>
@@ -8440,68 +8446,68 @@
       </c>
       <c r="I37" s="42"/>
     </row>
-    <row r="38" spans="1:9" ht="31.5">
+    <row r="38" spans="1:9" ht="31">
       <c r="A38" s="38">
         <v>11</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D38" s="39" t="s">
         <v>154</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G38" s="39">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="H38" s="48">
         <f t="shared" si="0"/>
-        <v>8400</v>
+        <v>6600</v>
       </c>
       <c r="I38" s="42"/>
     </row>
-    <row r="39" spans="1:9" ht="31.5">
+    <row r="39" spans="1:9" ht="31">
       <c r="A39" s="38">
         <v>12</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="D39" s="39" t="s">
         <v>154</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F39" s="39" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="G39" s="39">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="H39" s="48">
         <f t="shared" si="0"/>
-        <v>12600</v>
+        <v>8400</v>
       </c>
       <c r="I39" s="42"/>
     </row>
-    <row r="40" spans="1:9" ht="31.5">
+    <row r="40" spans="1:9" ht="31">
       <c r="A40" s="38">
         <v>13</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C40" s="39" t="s">
         <v>6</v>
@@ -8524,24 +8530,24 @@
       </c>
       <c r="I40" s="42"/>
     </row>
-    <row r="41" spans="1:9" ht="31.5">
+    <row r="41" spans="1:9" ht="31">
       <c r="A41" s="38">
         <v>14</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="D41" s="39" t="s">
         <v>154</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="G41" s="39">
         <v>210</v>
@@ -8552,51 +8558,79 @@
       </c>
       <c r="I41" s="42"/>
     </row>
-    <row r="42" spans="1:9" ht="21">
-      <c r="A42" s="84" t="s">
+    <row r="42" spans="1:9" ht="31">
+      <c r="A42" s="38">
+        <v>15</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="G42" s="39">
+        <v>210</v>
+      </c>
+      <c r="H42" s="48">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="I42" s="42"/>
+    </row>
+    <row r="43" spans="1:9" ht="21">
+      <c r="A43" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="85"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="85"/>
+      <c r="H43" s="85"/>
+      <c r="I43" s="86"/>
+    </row>
+    <row r="44" spans="1:9" ht="38.15" customHeight="1" thickBot="1">
+      <c r="A44" s="43">
+        <v>1</v>
+      </c>
+      <c r="B44" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="86"/>
-    </row>
-    <row r="43" spans="1:9" ht="38.1" customHeight="1" thickBot="1">
-      <c r="A43" s="43">
-        <v>1</v>
-      </c>
-      <c r="B43" s="44" t="s">
+      <c r="C44" s="44"/>
+      <c r="D44" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="45" t="s">
+      <c r="E44" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E43" s="44" t="s">
+      <c r="F44" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="G43" s="45">
+      <c r="G44" s="45">
         <v>215</v>
       </c>
-      <c r="H43" s="49">
+      <c r="H44" s="49">
         <f t="shared" si="0"/>
         <v>12900</v>
       </c>
-      <c r="I43" s="46"/>
+      <c r="I44" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/PHIẾU ĐĂNG KÝ TĂNG CA.xlsx
+++ b/docs/PHIẾU ĐĂNG KÝ TĂNG CA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hansungbolt-overtime\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79243FE2-8D77-4E84-956E-E1F0FB786D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68739A81-6B10-4693-9632-327D23B91A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="-50" windowWidth="38500" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-50" yWindow="-50" windowWidth="38500" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HD" sheetId="9" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="175">
   <si>
     <t>STT
 No.</t>
@@ -1346,8 +1346,125 @@
 (JAPAN)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Total: 42 MC </t>
+    <t>RL-02</t>
+  </si>
+  <si>
+    <t>ROLLING</t>
+  </si>
+  <si>
+    <t>FR 120406 
+KOREA MACHINERY (KOREA)</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>DPR-10S
+CHUN ZU (KOREA)</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>JSR-M8
+JIN SAN (KOREA)</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>RL-05~08
+(4EA)</t>
+  </si>
+  <si>
+    <t>JSR-M6
+JIN SAN (KOREA)</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>RL-09~14
+(6EA)</t>
+  </si>
+  <si>
+    <t>ROLLING
+(T/S-1)</t>
+  </si>
+  <si>
+    <t>JSR-M4
+JIN SAN (KOREA)</t>
+  </si>
+  <si>
+    <t>RL-15~23
+(9EA)</t>
+  </si>
+  <si>
+    <t>RL-40~42
+(3EA)</t>
+  </si>
+  <si>
+    <t>JSR-M3
+JIN SAN (KOREA)</t>
+  </si>
+  <si>
+    <t>SM-01</t>
+  </si>
+  <si>
+    <t>SEM ROLLING</t>
+  </si>
+  <si>
+    <t>THI-12R
+SAN MEI (TAIWAN)</t>
+  </si>
+  <si>
+    <t>SM-2A</t>
+  </si>
+  <si>
+    <t>SM-06</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CT-01~06
+(6EA)</t>
+  </si>
+  <si>
+    <t>CUTTING</t>
+  </si>
+  <si>
+    <t>TAE HUNG</t>
+  </si>
+  <si>
+    <t>M3-M6</t>
+  </si>
+  <si>
+    <t>Quy cách</t>
+  </si>
+  <si>
+    <t>Số lượng sản xuất 1 tiếng</t>
+  </si>
+  <si>
+    <t>VỆ SINH
+MÁY LẠNH</t>
+  </si>
+  <si>
+    <t>Dự kiến
+4 ngày</t>
+  </si>
+  <si>
+    <t>9/14 EA</t>
+  </si>
+  <si>
+    <t>RL-24</t>
+  </si>
+  <si>
+    <t>FUJIU MACHINERY FACTORY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Total: 33 MC </t>
     </r>
     <r>
       <rPr>
@@ -1358,129 +1475,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>( 8 Former &amp; 34 Header)</t>
-    </r>
-  </si>
-  <si>
-    <t>RL-02</t>
-  </si>
-  <si>
-    <t>ROLLING</t>
-  </si>
-  <si>
-    <t>FR 120406 
-KOREA MACHINERY (KOREA)</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>DPR-10S
-CHUN ZU (KOREA)</t>
-  </si>
-  <si>
-    <t>M10</t>
-  </si>
-  <si>
-    <t>JSR-M8
-JIN SAN (KOREA)</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
-    <t>RL-05~08
-(4EA)</t>
-  </si>
-  <si>
-    <t>JSR-M6
-JIN SAN (KOREA)</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
-    <t>RL-09~14
-(6EA)</t>
-  </si>
-  <si>
-    <t>ROLLING
-(T/S-1)</t>
-  </si>
-  <si>
-    <t>JSR-M4
-JIN SAN (KOREA)</t>
-  </si>
-  <si>
-    <t>RL-15~23
-(9EA)</t>
-  </si>
-  <si>
-    <t>RL-40~42
-(3EA)</t>
-  </si>
-  <si>
-    <t>JSR-M3
-JIN SAN (KOREA)</t>
-  </si>
-  <si>
-    <t>SM-01</t>
-  </si>
-  <si>
-    <t>SEM ROLLING</t>
-  </si>
-  <si>
-    <t>THI-12R
-SAN MEI (TAIWAN)</t>
-  </si>
-  <si>
-    <t>SM-2A</t>
-  </si>
-  <si>
-    <t>SM-06</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>CT-01~06
-(6EA)</t>
-  </si>
-  <si>
-    <t>CUTTING</t>
-  </si>
-  <si>
-    <t>TAE HUNG</t>
-  </si>
-  <si>
-    <t>M3-M6</t>
-  </si>
-  <si>
-    <t>Quy cách</t>
-  </si>
-  <si>
-    <t>Số lượng sản xuất 1 tiếng</t>
-  </si>
-  <si>
-    <t>VỆ SINH
-MÁY LẠNH</t>
-  </si>
-  <si>
-    <t>Dự kiến
-4 ngày</t>
-  </si>
-  <si>
-    <t>9/14 EA</t>
-  </si>
-  <si>
-    <t>RL-24</t>
-  </si>
-  <si>
-    <t>FUJIU MACHINERY FACTORY</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Total: 33 MC </t>
+      <t>( 26 RL &amp; 7 SM)</t>
+    </r>
+  </si>
+  <si>
+    <t>HD-1A</t>
+  </si>
+  <si>
+    <t>M16 / 4D4B</t>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>HWANSEUNG ENG.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Total: 43 MC </t>
     </r>
     <r>
       <rPr>
@@ -1491,7 +1503,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>( 26 RL &amp; 7 SM)</t>
+      <t>( 8 Former &amp; 34 Header)</t>
     </r>
   </si>
 </sst>
@@ -3888,8 +3900,44 @@
     <xf numFmtId="0" fontId="106" fillId="50" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="49" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="49" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3933,24 +3981,6 @@
     <xf numFmtId="20" fontId="108" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3972,25 +4002,7 @@
     <xf numFmtId="0" fontId="119" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="49" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="49" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6467,78 +6479,78 @@
       <c r="B3" s="13"/>
     </row>
     <row r="4" spans="2:20" s="14" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
       <c r="O4" s="26"/>
     </row>
     <row r="5" spans="2:20" s="14" customFormat="1" ht="31" customHeight="1">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="70" t="s">
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="72"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="64"/>
     </row>
     <row r="6" spans="2:20" ht="9" customHeight="1"/>
     <row r="7" spans="2:20" ht="38.5" customHeight="1">
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68" t="s">
+      <c r="E7" s="60"/>
+      <c r="F7" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68" t="s">
+      <c r="G7" s="60"/>
+      <c r="H7" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="68" t="s">
+      <c r="I7" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="68" t="s">
+      <c r="J7" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="68" t="s">
+      <c r="K7" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="68" t="s">
+      <c r="L7" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="60" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="42.65" customHeight="1">
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="15" t="s">
         <v>56</v>
       </c>
@@ -6551,28 +6563,28 @@
       <c r="G8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
     </row>
     <row r="9" spans="2:20" ht="32.15" customHeight="1">
-      <c r="B9" s="53">
+      <c r="B9" s="65">
         <v>1</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="61" t="s">
+      <c r="E9" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
       <c r="H9" s="15" t="s">
         <v>36</v>
       </c>
@@ -6588,12 +6600,12 @@
       <c r="M9" s="27"/>
     </row>
     <row r="10" spans="2:20" ht="32.15" customHeight="1">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
       <c r="H10" s="15" t="s">
         <v>73</v>
       </c>
@@ -6609,12 +6621,12 @@
       <c r="M10" s="27"/>
     </row>
     <row r="11" spans="2:20" ht="32.15" customHeight="1">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
       <c r="H11" s="15" t="s">
         <v>28</v>
       </c>
@@ -6630,12 +6642,12 @@
       <c r="M11" s="27"/>
     </row>
     <row r="12" spans="2:20" ht="32.15" customHeight="1">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="15" t="s">
         <v>76</v>
       </c>
@@ -6651,12 +6663,12 @@
       <c r="M12" s="27"/>
     </row>
     <row r="13" spans="2:20" ht="32.15" customHeight="1">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
       <c r="H13" s="15" t="s">
         <v>79</v>
       </c>
@@ -6736,67 +6748,75 @@
       </c>
     </row>
     <row r="17" spans="2:13" s="11" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
     </row>
     <row r="18" spans="2:13" s="11" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
     </row>
     <row r="19" spans="2:13" s="11" customFormat="1" ht="3.75" customHeight="1">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
-      <c r="L19" s="56"/>
-      <c r="M19" s="56"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
     </row>
     <row r="20" spans="2:13" s="11" customFormat="1" ht="33" customHeight="1">
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1"/>
     <row r="22" spans="2:13" ht="5.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="B19:M20"/>
+    <mergeCell ref="B17:M18"/>
+    <mergeCell ref="G9:G13"/>
+    <mergeCell ref="F9:F13"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="C9:C13"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
@@ -6810,14 +6830,6 @@
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="B19:M20"/>
-    <mergeCell ref="B17:M18"/>
-    <mergeCell ref="G9:G13"/>
-    <mergeCell ref="F9:F13"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="C9:C13"/>
   </mergeCells>
   <phoneticPr fontId="118" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6862,79 +6874,79 @@
       <c r="B3" s="13"/>
     </row>
     <row r="4" spans="1:22" s="14" customFormat="1" ht="65.5" customHeight="1">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
     </row>
     <row r="5" spans="1:22" s="14" customFormat="1" ht="38.25" customHeight="1">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="70" t="s">
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="72"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="64"/>
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:22" ht="9" customHeight="1"/>
     <row r="7" spans="1:22" ht="38.5" customHeight="1">
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68" t="s">
+      <c r="E7" s="60"/>
+      <c r="F7" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68" t="s">
+      <c r="G7" s="60"/>
+      <c r="H7" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="68" t="s">
+      <c r="I7" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="68" t="s">
+      <c r="J7" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="68" t="s">
+      <c r="K7" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="68" t="s">
+      <c r="L7" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="60" t="s">
         <v>5</v>
       </c>
       <c r="P7" s="26"/>
     </row>
     <row r="8" spans="1:22" ht="42.65" customHeight="1">
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="15" t="s">
         <v>56</v>
       </c>
@@ -6947,29 +6959,29 @@
       <c r="G8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
       <c r="O8" s="26"/>
     </row>
     <row r="9" spans="1:22" ht="25" customHeight="1">
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="75"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="81"/>
     </row>
     <row r="10" spans="1:22" ht="28.5" customHeight="1">
       <c r="A10" s="20"/>
@@ -6987,17 +6999,17 @@
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="29"/>
-      <c r="H10" s="76" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="78" t="s">
-        <v>167</v>
+      <c r="H10" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="I10" s="84" t="s">
+        <v>166</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="21"/>
       <c r="L10" s="25"/>
-      <c r="M10" s="78" t="s">
-        <v>166</v>
+      <c r="M10" s="84" t="s">
+        <v>165</v>
       </c>
       <c r="P10" s="23"/>
     </row>
@@ -7017,12 +7029,12 @@
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="79"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="85"/>
       <c r="J11" s="22"/>
       <c r="K11" s="21"/>
       <c r="L11" s="25"/>
-      <c r="M11" s="79"/>
+      <c r="M11" s="85"/>
       <c r="P11" s="23"/>
     </row>
     <row r="12" spans="1:22" ht="71.25" customHeight="1">
@@ -7034,67 +7046,73 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="11" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="69"/>
     </row>
     <row r="14" spans="1:22" s="11" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="15" spans="1:22" s="11" customFormat="1" ht="3.75" customHeight="1">
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="56"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="56"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
     </row>
     <row r="16" spans="1:22" s="11" customFormat="1" ht="33" customHeight="1">
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
     </row>
     <row r="17" ht="17.25" customHeight="1"/>
     <row r="18" ht="5.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B15:M16"/>
+    <mergeCell ref="B13:M14"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="I10:I11"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="H5:M5"/>
@@ -7108,12 +7126,6 @@
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B15:M16"/>
-    <mergeCell ref="B13:M14"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="I10:I11"/>
   </mergeCells>
   <phoneticPr fontId="118" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7137,11 +7149,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="46">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
     </row>
     <row r="2" spans="1:3" s="5" customFormat="1">
       <c r="A2" s="4" t="s">
@@ -7472,7 +7484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEB8C6C-2C8B-4474-AB53-38C0EB5023E6}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="7.54296875" style="30" customWidth="1"/>
@@ -7488,23 +7500,23 @@
   <sheetData>
     <row r="1" spans="1:9" ht="13" thickBot="1"/>
     <row r="2" spans="1:9" ht="44" thickBot="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="82"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="54"/>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="83"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
     </row>
@@ -7516,7 +7528,7 @@
         <v>88</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>89</v>
@@ -7531,7 +7543,7 @@
         <v>92</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I4" s="36" t="s">
         <v>93</v>
@@ -7545,7 +7557,7 @@
         <v>94</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" s="40" t="s">
         <v>95</v>
@@ -7570,26 +7582,26 @@
         <v>2</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>99</v>
+        <v>172</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>173</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="G6" s="39">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H6" s="48">
-        <f t="shared" ref="H6:H44" si="0">G6*60</f>
-        <v>2700</v>
+        <f>G6*60</f>
+        <v>3000</v>
       </c>
       <c r="I6" s="42"/>
     </row>
@@ -7598,26 +7610,26 @@
         <v>3</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>102</v>
+        <v>140</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>99</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G7" s="39">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H7" s="48">
-        <f t="shared" si="0"/>
-        <v>5400</v>
+        <f t="shared" ref="H7:H45" si="0">G7*60</f>
+        <v>2700</v>
       </c>
       <c r="I7" s="42"/>
     </row>
@@ -7626,19 +7638,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" s="40" t="s">
         <v>95</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G8" s="39">
         <v>90</v>
@@ -7654,16 +7666,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="40" t="s">
         <v>95</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F9" s="39" t="s">
         <v>106</v>
@@ -7682,26 +7694,26 @@
         <v>6</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>98</v>
+        <v>140</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>95</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G10" s="39">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="H10" s="48">
         <f t="shared" si="0"/>
-        <v>3300</v>
+        <v>5400</v>
       </c>
       <c r="I10" s="42"/>
     </row>
@@ -7710,26 +7722,26 @@
         <v>7</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" s="39" t="s">
         <v>98</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G11" s="39">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H11" s="48">
         <f t="shared" si="0"/>
-        <v>2700</v>
+        <v>3300</v>
       </c>
       <c r="I11" s="42"/>
     </row>
@@ -7738,26 +7750,26 @@
         <v>8</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>95</v>
+        <v>140</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>98</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G12" s="39">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="H12" s="48">
         <f t="shared" si="0"/>
-        <v>8400</v>
+        <v>2700</v>
       </c>
       <c r="I12" s="42"/>
     </row>
@@ -7766,16 +7778,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13" s="40" t="s">
         <v>95</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F13" s="39" t="s">
         <v>112</v>
@@ -7794,26 +7806,26 @@
         <v>10</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>98</v>
+        <v>142</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>95</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G14" s="39">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="H14" s="48">
         <f t="shared" si="0"/>
-        <v>3300</v>
+        <v>8400</v>
       </c>
       <c r="I14" s="42"/>
     </row>
@@ -7822,16 +7834,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F15" s="39" t="s">
         <v>115</v>
@@ -7850,26 +7862,26 @@
         <v>12</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G16" s="39">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H16" s="48">
         <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>3300</v>
       </c>
       <c r="I16" s="42"/>
     </row>
@@ -7878,26 +7890,26 @@
         <v>13</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>95</v>
+        <v>145</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>98</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G17" s="39">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H17" s="48">
         <f t="shared" si="0"/>
-        <v>6900</v>
+        <v>4200</v>
       </c>
       <c r="I17" s="42"/>
     </row>
@@ -7906,26 +7918,26 @@
         <v>14</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D18" s="40" t="s">
         <v>95</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G18" s="39">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="H18" s="48">
         <f t="shared" si="0"/>
-        <v>16800</v>
+        <v>6900</v>
       </c>
       <c r="I18" s="42"/>
     </row>
@@ -7934,26 +7946,26 @@
         <v>15</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>123</v>
+        <v>145</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>121</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G19" s="39">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="H19" s="48">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>16800</v>
       </c>
       <c r="I19" s="42"/>
     </row>
@@ -7962,26 +7974,26 @@
         <v>16</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D20" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="41" t="s">
-        <v>125</v>
+      <c r="E20" s="39" t="s">
+        <v>123</v>
       </c>
       <c r="F20" s="39" t="s">
         <v>124</v>
       </c>
       <c r="G20" s="39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H20" s="48">
         <f t="shared" si="0"/>
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="I20" s="42"/>
     </row>
@@ -7990,16 +8002,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="41" t="s">
         <v>98</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21" s="39" t="s">
         <v>124</v>
@@ -8018,10 +8030,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D22" s="41" t="s">
         <v>98</v>
@@ -8046,10 +8058,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D23" s="41" t="s">
         <v>98</v>
@@ -8073,27 +8085,27 @@
       <c r="A24" s="38">
         <v>20</v>
       </c>
-      <c r="B24" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>6</v>
+      <c r="B24" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>145</v>
       </c>
       <c r="D24" s="41" t="s">
         <v>98</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G24" s="39">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="H24" s="48">
         <f t="shared" si="0"/>
-        <v>10800</v>
+        <v>6600</v>
       </c>
       <c r="I24" s="42"/>
     </row>
@@ -8102,19 +8114,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="D25" s="41" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G25" s="39">
         <v>180</v>
@@ -8130,16 +8142,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26" s="41" t="s">
         <v>98</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F26" s="39" t="s">
         <v>132</v>
@@ -8153,121 +8165,121 @@
       </c>
       <c r="I26" s="42"/>
     </row>
-    <row r="27" spans="1:9" ht="24" customHeight="1">
-      <c r="A27" s="84" t="s">
+    <row r="27" spans="1:9" ht="36" customHeight="1">
+      <c r="A27" s="38">
+        <v>23</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="39">
+        <v>180</v>
+      </c>
+      <c r="H27" s="48">
+        <f t="shared" si="0"/>
+        <v>10800</v>
+      </c>
+      <c r="I27" s="42"/>
+    </row>
+    <row r="28" spans="1:9" ht="24" customHeight="1">
+      <c r="A28" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="58"/>
+    </row>
+    <row r="29" spans="1:9" ht="31">
+      <c r="A29" s="38">
+        <v>1</v>
+      </c>
+      <c r="B29" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="85"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="86"/>
-    </row>
-    <row r="28" spans="1:9" ht="31">
-      <c r="A28" s="38">
-        <v>1</v>
-      </c>
-      <c r="B28" s="39" t="s">
+      <c r="C29" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="C28" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="D28" s="39" t="s">
+      <c r="E29" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="E28" s="41" t="s">
+      <c r="F29" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="G28" s="39">
+      <c r="G29" s="39">
         <v>80</v>
       </c>
-      <c r="H28" s="48">
+      <c r="H29" s="48">
         <f t="shared" si="0"/>
         <v>4800</v>
       </c>
-      <c r="I28" s="42"/>
-    </row>
-    <row r="29" spans="1:9" ht="31">
-      <c r="A29" s="38">
+      <c r="I29" s="42"/>
+    </row>
+    <row r="30" spans="1:9" ht="31">
+      <c r="A30" s="38">
         <v>2</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B30" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" s="41" t="s">
+      <c r="C30" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="F29" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="G29" s="39">
+      <c r="D30" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" s="39">
         <v>102</v>
       </c>
-      <c r="H29" s="48">
+      <c r="H30" s="48">
         <f t="shared" si="0"/>
         <v>6120</v>
       </c>
-      <c r="I29" s="42"/>
-    </row>
-    <row r="30" spans="1:9" ht="31">
-      <c r="A30" s="38">
-        <v>3</v>
-      </c>
-      <c r="B30" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="39">
-        <v>140</v>
-      </c>
-      <c r="H30" s="48">
-        <f t="shared" si="0"/>
-        <v>8400</v>
-      </c>
       <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9" ht="31">
       <c r="A31" s="38">
-        <v>4</v>
-      </c>
-      <c r="B31" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>146</v>
+        <v>3</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>142</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G31" s="39">
         <v>140</v>
@@ -8280,47 +8292,47 @@
     </row>
     <row r="32" spans="1:9" ht="31">
       <c r="A32" s="38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>148</v>
+        <v>145</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>136</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="G32" s="39">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="H32" s="48">
         <f t="shared" si="0"/>
-        <v>12900</v>
+        <v>8400</v>
       </c>
       <c r="I32" s="42"/>
     </row>
     <row r="33" spans="1:9" ht="31">
       <c r="A33" s="38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="39" t="s">
-        <v>137</v>
+      <c r="D33" s="41" t="s">
+        <v>147</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F33" s="39" t="s">
         <v>6</v>
@@ -8334,136 +8346,136 @@
       </c>
       <c r="I33" s="42"/>
     </row>
-    <row r="34" spans="1:9" ht="36" customHeight="1">
+    <row r="34" spans="1:9" ht="31">
       <c r="A34" s="38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C34" s="41" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F34" s="39" t="s">
         <v>6</v>
       </c>
       <c r="G34" s="39">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="H34" s="48">
         <f t="shared" si="0"/>
-        <v>3600</v>
+        <v>12900</v>
       </c>
       <c r="I34" s="42"/>
     </row>
-    <row r="35" spans="1:9" ht="31">
+    <row r="35" spans="1:9" ht="36" customHeight="1">
       <c r="A35" s="38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F35" s="39" t="s">
         <v>6</v>
       </c>
       <c r="G35" s="39">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="H35" s="48">
         <f t="shared" si="0"/>
-        <v>21000</v>
+        <v>3600</v>
       </c>
       <c r="I35" s="42"/>
     </row>
     <row r="36" spans="1:9" ht="31">
       <c r="A36" s="38">
-        <v>9</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>139</v>
+        <v>8</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>157</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="G36" s="39">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="H36" s="48">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="I36" s="42"/>
     </row>
     <row r="37" spans="1:9" ht="31">
       <c r="A37" s="38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D37" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="E37" s="41" t="s">
-        <v>142</v>
-      </c>
       <c r="F37" s="39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G37" s="39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H37" s="48">
         <f t="shared" si="0"/>
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:9" ht="31">
       <c r="A38" s="38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E38" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="39" t="s">
         <v>142</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>143</v>
       </c>
       <c r="G38" s="39">
         <v>110</v>
@@ -8476,75 +8488,75 @@
     </row>
     <row r="39" spans="1:9" ht="31">
       <c r="A39" s="38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F39" s="39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G39" s="39">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="H39" s="48">
         <f t="shared" si="0"/>
-        <v>8400</v>
+        <v>6600</v>
       </c>
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" ht="31">
       <c r="A40" s="38">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="G40" s="39">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="H40" s="48">
         <f t="shared" si="0"/>
-        <v>12600</v>
+        <v>8400</v>
       </c>
       <c r="I40" s="42"/>
     </row>
     <row r="41" spans="1:9" ht="31">
       <c r="A41" s="38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C41" s="39" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="39" t="s">
         <v>6</v>
@@ -8560,22 +8572,22 @@
     </row>
     <row r="42" spans="1:9" ht="31">
       <c r="A42" s="38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E42" s="41" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="G42" s="39">
         <v>210</v>
@@ -8586,51 +8598,79 @@
       </c>
       <c r="I42" s="42"/>
     </row>
-    <row r="43" spans="1:9" ht="21">
-      <c r="A43" s="84" t="s">
-        <v>170</v>
-      </c>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="86"/>
-    </row>
-    <row r="44" spans="1:9" ht="38.15" customHeight="1" thickBot="1">
-      <c r="A44" s="43">
+    <row r="43" spans="1:9" ht="31">
+      <c r="A43" s="38">
+        <v>15</v>
+      </c>
+      <c r="B43" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="G43" s="39">
+        <v>210</v>
+      </c>
+      <c r="H43" s="48">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="I43" s="42"/>
+    </row>
+    <row r="44" spans="1:9" ht="21">
+      <c r="A44" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="58"/>
+    </row>
+    <row r="45" spans="1:9" ht="38.15" customHeight="1" thickBot="1">
+      <c r="A45" s="43">
         <v>1</v>
       </c>
-      <c r="B44" s="44" t="s">
+      <c r="B45" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="44"/>
+      <c r="D45" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="C44" s="44"/>
-      <c r="D44" s="45" t="s">
+      <c r="E45" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="44" t="s">
+      <c r="F45" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="F44" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="G44" s="45">
+      <c r="G45" s="45">
         <v>215</v>
       </c>
-      <c r="H44" s="49">
+      <c r="H45" s="49">
         <f t="shared" si="0"/>
         <v>12900</v>
       </c>
-      <c r="I44" s="46"/>
+      <c r="I45" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A44:I44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
